--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9775,0.0103,0.0033,0.0041</t>
-  </si>
-  <si>
-    <t>0.0114,0.0013,0.0008,0.9951</t>
-  </si>
-  <si>
-    <t>0.7631,0.0017,0.0007,0.3640</t>
-  </si>
-  <si>
-    <t>0.1012,0.0032,0.0000,0.9452</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0010,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9890,0.0112,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9963,0.0016,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9089,0.0498,0.0398,0.0033</t>
-  </si>
-  <si>
-    <t>0.3430,0.0090,0.7985,0.0005</t>
-  </si>
-  <si>
-    <t>0.7630,0.0121,0.3168,0.0002</t>
-  </si>
-  <si>
-    <t>0.0158,0.0039,0.9811,0.0013</t>
-  </si>
-  <si>
-    <t>0.9943,0.0010,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.9956,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0036,0.9900,0.0025,0.0033</t>
-  </si>
-  <si>
-    <t>0.2745,0.8263,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.0669,0.9489,0.0037,0.0011</t>
-  </si>
-  <si>
-    <t>0.0026,0.9937,0.0058,0.0012</t>
-  </si>
-  <si>
-    <t>0.1703,0.0106,0.8614,0.0098</t>
-  </si>
-  <si>
-    <t>0.6801,0.0020,0.5820,0.0009</t>
-  </si>
-  <si>
-    <t>0.0265,0.0009,0.9847,0.0003</t>
-  </si>
-  <si>
-    <t>0.0101,0.0057,0.9728,0.0091</t>
-  </si>
-  <si>
-    <t>0.1031,0.0017,0.9485,0.0021</t>
-  </si>
-  <si>
-    <t>0.0305,0.0163,0.9465,0.0105</t>
-  </si>
-  <si>
-    <t>0.0489,0.0018,0.9717,0.0013</t>
-  </si>
-  <si>
-    <t>0.2165,0.8863,0.0025,0.0012</t>
-  </si>
-  <si>
-    <t>0.2746,0.7201,0.0585,0.0027</t>
-  </si>
-  <si>
-    <t>0.0020,0.0010,0.9925,0.0078</t>
-  </si>
-  <si>
-    <t>0.0043,0.9881,0.0096,0.0006</t>
-  </si>
-  <si>
-    <t>0.9816,0.0099,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.9916,0.0029,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.3151,0.7752,0.0042,0.0048</t>
-  </si>
-  <si>
-    <t>0.0079,0.9602,0.0447,0.0242</t>
-  </si>
-  <si>
-    <t>0.0577,0.4643,0.3172,0.0125</t>
-  </si>
-  <si>
-    <t>0.6313,0.0037,0.2773,0.0296</t>
-  </si>
-  <si>
-    <t>0.0210,0.0355,0.9534,0.0220</t>
-  </si>
-  <si>
-    <t>0.0579,0.0011,0.9472,0.0086</t>
-  </si>
-  <si>
-    <t>0.0122,0.1433,0.9630,0.0028</t>
-  </si>
-  <si>
-    <t>0.0249,0.9355,0.0178,0.0038</t>
-  </si>
-  <si>
-    <t>0.0089,0.0043,0.9873,0.0018</t>
-  </si>
-  <si>
-    <t>0.0153,0.7482,0.0164,0.7426</t>
-  </si>
-  <si>
-    <t>0.0063,0.9750,0.0024,0.0180</t>
-  </si>
-  <si>
-    <t>0.0028,0.9858,0.0091,0.0043</t>
-  </si>
-  <si>
-    <t>0.0021,0.9744,0.0364,0.0166</t>
-  </si>
-  <si>
-    <t>0.0143,0.0049,0.9823,0.0019</t>
-  </si>
-  <si>
-    <t>0.0048,0.0844,0.9696,0.0038</t>
-  </si>
-  <si>
-    <t>0.0128,0.0024,0.9852,0.0013</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9974,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.0012,0.9912,0.0063</t>
-  </si>
-  <si>
-    <t>0.0375,0.0444,0.9299,0.0016</t>
-  </si>
-  <si>
-    <t>0.9940,0.0042,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0007,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9940,0.0015,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.0055,0.0020,0.9923,0.0029</t>
-  </si>
-  <si>
-    <t>0.9881,0.0046,0.0035,0.0019</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9768,0.0278,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.0017,0.6087,0.9772,0.0014</t>
-  </si>
-  <si>
-    <t>0.0192,0.0073,0.9820,0.0025</t>
-  </si>
-  <si>
-    <t>0.0018,0.0011,0.9960,0.0016</t>
-  </si>
-  <si>
-    <t>0.0014,0.8273,0.9340,0.0039</t>
-  </si>
-  <si>
-    <t>0.0026,0.0006,0.9954,0.0019</t>
-  </si>
-  <si>
-    <t>0.1509,0.9167,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.0090,0.9904,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9758,0.0033,0.0131,0.0047</t>
-  </si>
-  <si>
-    <t>0.2107,0.0953,0.7604,0.0236</t>
-  </si>
-  <si>
-    <t>0.0025,0.0048,0.9945,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9689,0.9537,0.0002</t>
-  </si>
-  <si>
-    <t>0.0046,0.7230,0.8919,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9937,0.7524,0.0003</t>
-  </si>
-  <si>
-    <t>0.0599,0.0004,0.0083,0.9550</t>
-  </si>
-  <si>
-    <t>0.0020,0.0009,0.0004,0.9988</t>
-  </si>
-  <si>
-    <t>0.0169,0.0004,0.0002,0.9956</t>
-  </si>
-  <si>
-    <t>0.0289,0.0004,0.0007,0.9906</t>
-  </si>
-  <si>
-    <t>0.0183,0.0004,0.0039,0.9882</t>
-  </si>
-  <si>
-    <t>0.0075,0.0017,0.0014,0.9952</t>
-  </si>
-  <si>
-    <t>0.0008,0.9488,0.9675,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.1391,0.9844,0.0017</t>
-  </si>
-  <si>
-    <t>0.0058,0.9555,0.0773,0.0111</t>
-  </si>
-  <si>
-    <t>0.0291,0.1409,0.9171,0.0345</t>
-  </si>
-  <si>
-    <t>0.0027,0.8603,0.9350,0.0010</t>
-  </si>
-  <si>
-    <t>0.0049,0.9684,0.1922,0.0025</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0023,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9923,0.0089,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0020,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0022,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9909,0.0087,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0018,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0003,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.0197,0.0002,0.9902,0.0005</t>
-  </si>
-  <si>
-    <t>0.0206,0.0119,0.9494,0.0173</t>
-  </si>
-  <si>
-    <t>0.9845,0.0012,0.0029,0.0046</t>
-  </si>
-  <si>
-    <t>0.1233,0.0017,0.9425,0.0011</t>
-  </si>
-  <si>
-    <t>0.0130,0.9806,0.0096,0.0013</t>
-  </si>
-  <si>
-    <t>0.0024,0.9923,0.0050,0.0011</t>
-  </si>
-  <si>
-    <t>0.0737,0.9487,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.0663,0.9359,0.0116,0.0026</t>
-  </si>
-  <si>
-    <t>0.0032,0.9913,0.0031,0.0019</t>
-  </si>
-  <si>
-    <t>0.0025,0.9933,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.7182,0.4164,0.0048,0.0014</t>
-  </si>
-  <si>
-    <t>0.9241,0.0210,0.0638,0.0039</t>
-  </si>
-  <si>
-    <t>0.8889,0.0054,0.1817,0.0025</t>
-  </si>
-  <si>
-    <t>0.8599,0.0122,0.0932,0.0173</t>
-  </si>
-  <si>
-    <t>0.5430,0.0136,0.5802,0.0020</t>
-  </si>
-  <si>
-    <t>0.1511,0.0186,0.0282,0.8818</t>
-  </si>
-  <si>
-    <t>0.0026,0.9956,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.9887,0.0018,0.0026</t>
-  </si>
-  <si>
-    <t>0.0003,0.9962,0.0093,0.0069</t>
-  </si>
-  <si>
-    <t>0.0009,0.6965,0.9804,0.0018</t>
-  </si>
-  <si>
-    <t>0.0056,0.9926,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.6401,0.4247,0.0287,0.0049</t>
-  </si>
-  <si>
-    <t>0.9398,0.0665,0.0028,0.0023</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9950,0.0006,0.0020,0.0010</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9780,0.0042,0.0041,0.0093</t>
+  </si>
+  <si>
+    <t>0.0863,0.0016,0.0011,0.9709</t>
+  </si>
+  <si>
+    <t>0.7892,0.0027,0.0019,0.3373</t>
+  </si>
+  <si>
+    <t>0.0725,0.0043,0.0002,0.9709</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9947,0.0018,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9851,0.0139,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9920,0.0012,0.0003,0.0034</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.6971,0.0936,0.1972,0.0121</t>
+  </si>
+  <si>
+    <t>0.0493,0.0347,0.9255,0.0025</t>
+  </si>
+  <si>
+    <t>0.2617,0.0448,0.7557,0.0008</t>
+  </si>
+  <si>
+    <t>0.2453,0.0023,0.9039,0.0002</t>
+  </si>
+  <si>
+    <t>0.9840,0.0035,0.0127,0.0005</t>
+  </si>
+  <si>
+    <t>0.0228,0.9849,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.9921,0.0040,0.0008</t>
+  </si>
+  <si>
+    <t>0.0883,0.9241,0.0042,0.0023</t>
+  </si>
+  <si>
+    <t>0.1019,0.9169,0.0044,0.0103</t>
+  </si>
+  <si>
+    <t>0.0048,0.9890,0.0044,0.0021</t>
+  </si>
+  <si>
+    <t>0.7939,0.0034,0.1683,0.0181</t>
+  </si>
+  <si>
+    <t>0.9564,0.0017,0.0717,0.0007</t>
+  </si>
+  <si>
+    <t>0.0090,0.0011,0.9903,0.0008</t>
+  </si>
+  <si>
+    <t>0.0295,0.0042,0.9631,0.0048</t>
+  </si>
+  <si>
+    <t>0.0394,0.0024,0.9717,0.0025</t>
+  </si>
+  <si>
+    <t>0.0036,0.0046,0.9845,0.0097</t>
+  </si>
+  <si>
+    <t>0.0008,0.0007,0.9965,0.0034</t>
+  </si>
+  <si>
+    <t>0.6042,0.4740,0.0145,0.0009</t>
+  </si>
+  <si>
+    <t>0.6606,0.4601,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.0039,0.0023,0.9905,0.0047</t>
+  </si>
+  <si>
+    <t>0.0207,0.9844,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9479,0.0182,0.0016,0.0158</t>
+  </si>
+  <si>
+    <t>0.8606,0.0131,0.1562,0.0034</t>
+  </si>
+  <si>
+    <t>0.2196,0.8420,0.0024,0.0038</t>
+  </si>
+  <si>
+    <t>0.0076,0.9663,0.0273,0.0216</t>
+  </si>
+  <si>
+    <t>0.0376,0.0644,0.9089,0.0068</t>
+  </si>
+  <si>
+    <t>0.0172,0.0038,0.9779,0.0077</t>
+  </si>
+  <si>
+    <t>0.0092,0.5483,0.9412,0.0153</t>
+  </si>
+  <si>
+    <t>0.1050,0.1568,0.8873,0.0125</t>
+  </si>
+  <si>
+    <t>0.0020,0.0344,0.9929,0.0006</t>
+  </si>
+  <si>
+    <t>0.0419,0.9080,0.0216,0.0029</t>
+  </si>
+  <si>
+    <t>0.0041,0.0007,0.9938,0.0011</t>
+  </si>
+  <si>
+    <t>0.0862,0.5382,0.0017,0.4516</t>
+  </si>
+  <si>
+    <t>0.0113,0.9418,0.0072,0.0454</t>
+  </si>
+  <si>
+    <t>0.0038,0.9800,0.0234,0.0036</t>
+  </si>
+  <si>
+    <t>0.0013,0.9557,0.0365,0.0498</t>
+  </si>
+  <si>
+    <t>0.0011,0.0030,0.9955,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.3091,0.9801,0.0038</t>
+  </si>
+  <si>
+    <t>0.2059,0.0113,0.8493,0.0063</t>
+  </si>
+  <si>
+    <t>0.0033,0.0011,0.9911,0.0062</t>
+  </si>
+  <si>
+    <t>0.0068,0.0034,0.9833,0.0072</t>
+  </si>
+  <si>
+    <t>0.0094,0.1893,0.9077,0.0020</t>
+  </si>
+  <si>
+    <t>0.9904,0.0085,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9959,0.0003,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0037,0.9962,0.0039</t>
+  </si>
+  <si>
+    <t>0.9934,0.0025,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0074,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.6755,0.9737,0.0010</t>
+  </si>
+  <si>
+    <t>0.0512,0.0310,0.9584,0.0040</t>
+  </si>
+  <si>
+    <t>0.0122,0.0517,0.9552,0.0288</t>
+  </si>
+  <si>
+    <t>0.0004,0.9574,0.9584,0.0009</t>
+  </si>
+  <si>
+    <t>0.0029,0.0009,0.9944,0.0020</t>
+  </si>
+  <si>
+    <t>0.3411,0.8311,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0081,0.9920,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0026,0.0074,0.0018</t>
+  </si>
+  <si>
+    <t>0.7685,0.0405,0.2411,0.0041</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.9955,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.9769,0.8770,0.0002</t>
+  </si>
+  <si>
+    <t>0.0061,0.9749,0.0824,0.0015</t>
+  </si>
+  <si>
+    <t>0.0022,0.9950,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0042,0.9664,0.3649,0.0028</t>
+  </si>
+  <si>
+    <t>0.0154,0.0010,0.0574,0.9617</t>
+  </si>
+  <si>
+    <t>0.0079,0.0008,0.0004,0.9968</t>
+  </si>
+  <si>
+    <t>0.0287,0.0047,0.0008,0.9887</t>
+  </si>
+  <si>
+    <t>0.0256,0.0004,0.0054,0.9811</t>
+  </si>
+  <si>
+    <t>0.0165,0.0020,0.0022,0.9907</t>
+  </si>
+  <si>
+    <t>0.0036,0.0010,0.0035,0.9958</t>
+  </si>
+  <si>
+    <t>0.0023,0.9725,0.7871,0.0024</t>
+  </si>
+  <si>
+    <t>0.0038,0.2037,0.9777,0.0016</t>
+  </si>
+  <si>
+    <t>0.0275,0.9358,0.0596,0.0054</t>
+  </si>
+  <si>
+    <t>0.0774,0.2101,0.7468,0.0038</t>
+  </si>
+  <si>
+    <t>0.0104,0.8843,0.7080,0.0032</t>
+  </si>
+  <si>
+    <t>0.0010,0.9879,0.3855,0.0018</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0071,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0048,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0046,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0018,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0044,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0021,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9952,0.0021,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0093,0.0004,0.9928,0.0012</t>
+  </si>
+  <si>
+    <t>0.0188,0.1572,0.9113,0.0091</t>
+  </si>
+  <si>
+    <t>0.9798,0.0022,0.0105,0.0018</t>
+  </si>
+  <si>
+    <t>0.0318,0.0017,0.9811,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.9921,0.0022,0.0011</t>
+  </si>
+  <si>
+    <t>0.0019,0.9917,0.0033,0.0038</t>
+  </si>
+  <si>
+    <t>0.0694,0.9464,0.0034,0.0024</t>
+  </si>
+  <si>
+    <t>0.0950,0.9110,0.0069,0.0054</t>
+  </si>
+  <si>
+    <t>0.0032,0.9902,0.0048,0.0025</t>
+  </si>
+  <si>
+    <t>0.0007,0.9972,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.2043,0.8320,0.0129,0.0022</t>
+  </si>
+  <si>
+    <t>0.9151,0.0289,0.0542,0.0050</t>
+  </si>
+  <si>
+    <t>0.4918,0.0063,0.5992,0.0121</t>
+  </si>
+  <si>
+    <t>0.2525,0.0868,0.5831,0.0154</t>
+  </si>
+  <si>
+    <t>0.1353,0.0119,0.8920,0.0049</t>
+  </si>
+  <si>
+    <t>0.1017,0.0870,0.0259,0.8827</t>
+  </si>
+  <si>
+    <t>0.0008,0.9946,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.0013,0.9911,0.0054,0.0038</t>
+  </si>
+  <si>
+    <t>0.0012,0.9884,0.0052,0.0647</t>
+  </si>
+  <si>
+    <t>0.0016,0.9188,0.6591,0.0090</t>
+  </si>
+  <si>
+    <t>0.0045,0.9915,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.5463,0.6129,0.0082,0.0024</t>
+  </si>
+  <si>
+    <t>0.9660,0.0433,0.0037,0.0007</t>
+  </si>
+  <si>
+    <t>0.9943,0.0016,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9963,0.0011,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9942,0.0012,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9941,0.0006,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0096,0.2279,0.9555,0.0014</t>
+  </si>
+  <si>
+    <t>0.0011,0.8498,0.9680,0.0002</t>
+  </si>
+  <si>
+    <t>0.0066,0.0233,0.9779,0.0009</t>
+  </si>
+  <si>
+    <t>0.0607,0.0536,0.8785,0.0127</t>
+  </si>
+  <si>
+    <t>0.9939,0.0004,0.0001,0.0035</t>
+  </si>
+  <si>
+    <t>0.9640,0.0021,0.0728,0.0006</t>
+  </si>
+  <si>
+    <t>0.1674,0.0015,0.9258,0.0011</t>
+  </si>
+  <si>
+    <t>0.7326,0.0080,0.3232,0.0083</t>
+  </si>
+  <si>
+    <t>0.1937,0.0010,0.0017,0.9366</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0026,0.9992</t>
+  </si>
+  <si>
+    <t>0.0007,0.0052,0.0007,0.9989</t>
+  </si>
+  <si>
+    <t>0.0246,0.0002,0.0026,0.9876</t>
+  </si>
+  <si>
+    <t>0.0018,0.9230,0.7080,0.0025</t>
+  </si>
+  <si>
+    <t>0.9963,0.0008,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0876,0.9281,0.0059,0.0040</t>
+  </si>
+  <si>
+    <t>0.9849,0.0054,0.0059,0.0015</t>
+  </si>
+  <si>
+    <t>0.8664,0.2402,0.0042,0.0013</t>
+  </si>
+  <si>
+    <t>0.9882,0.0010,0.0017,0.0055</t>
+  </si>
+  <si>
+    <t>0.7558,0.0040,0.0055,0.3719</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0026,0.0025,0.9602,0.1371</t>
+  </si>
+  <si>
+    <t>0.9729,0.0003,0.0002,0.0476</t>
+  </si>
+  <si>
+    <t>0.9435,0.0024,0.0004,0.0656</t>
+  </si>
+  <si>
+    <t>0.9084,0.1355,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9795,0.0085,0.0047,0.0023</t>
+  </si>
+  <si>
+    <t>0.9841,0.0124,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.0234,0.9573,0.0197,0.0047</t>
+  </si>
+  <si>
+    <t>0.9694,0.0161,0.0150,0.0010</t>
+  </si>
+  <si>
+    <t>0.9358,0.0624,0.0081,0.0036</t>
   </si>
   <si>
     <t>0.9976,0.0004,0.0002,0.0005</t>
   </si>
   <si>
-    <t>0.9948,0.0014,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9954,0.0003,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9968,0.0004,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0072,0.5202,0.9295,0.0012</t>
-  </si>
-  <si>
-    <t>0.0048,0.8773,0.7872,0.0040</t>
-  </si>
-  <si>
-    <t>0.0052,0.0127,0.9846,0.0008</t>
-  </si>
-  <si>
-    <t>0.0183,0.0518,0.9566,0.0041</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9245,0.0101,0.0710,0.0024</t>
-  </si>
-  <si>
-    <t>0.0846,0.0015,0.9526,0.0026</t>
-  </si>
-  <si>
-    <t>0.7449,0.0600,0.1805,0.0210</t>
-  </si>
-  <si>
-    <t>0.0507,0.0027,0.0016,0.9800</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.0014,0.9994</t>
-  </si>
-  <si>
-    <t>0.0018,0.0282,0.0024,0.9958</t>
-  </si>
-  <si>
-    <t>0.0124,0.0000,0.0001,0.9963</t>
-  </si>
-  <si>
-    <t>0.0020,0.9206,0.5130,0.0012</t>
-  </si>
-  <si>
-    <t>0.9964,0.0004,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.0465,0.9578,0.0036,0.0028</t>
-  </si>
-  <si>
-    <t>0.9828,0.0067,0.0045,0.0031</t>
-  </si>
-  <si>
-    <t>0.6763,0.4015,0.0060,0.0098</t>
-  </si>
-  <si>
-    <t>0.9956,0.0002,0.0004,0.0026</t>
-  </si>
-  <si>
-    <t>0.7876,0.0049,0.0051,0.3016</t>
-  </si>
-  <si>
-    <t>0.9962,0.0013,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.0054,0.8228,0.5844</t>
-  </si>
-  <si>
-    <t>0.8992,0.0003,0.0009,0.1996</t>
-  </si>
-  <si>
-    <t>0.9793,0.0006,0.0016,0.0161</t>
-  </si>
-  <si>
-    <t>0.8781,0.1691,0.0014,0.0036</t>
-  </si>
-  <si>
-    <t>0.9841,0.0064,0.0027,0.0018</t>
-  </si>
-  <si>
-    <t>0.9890,0.0060,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.7840,0.2155,0.0184,0.0057</t>
-  </si>
-  <si>
-    <t>0.9642,0.0105,0.0382,0.0004</t>
-  </si>
-  <si>
-    <t>0.9844,0.0072,0.0069,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0020,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9960,0.0014,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0002,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.6333,0.2886,0.0005,0.0077</t>
-  </si>
-  <si>
-    <t>0.6585,0.5557,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.8220,0.2247,0.0035,0.0052</t>
-  </si>
-  <si>
-    <t>0.9596,0.0133,0.0275,0.0043</t>
-  </si>
-  <si>
-    <t>0.9705,0.0260,0.0033,0.0018</t>
-  </si>
-  <si>
-    <t>0.9946,0.0041,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9831,0.0145,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.9652,0.0323,0.0049,0.0032</t>
-  </si>
-  <si>
-    <t>0.0009,0.0040,0.9974,0.0012</t>
-  </si>
-  <si>
-    <t>0.9932,0.0023,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.0077,0.9963,0.0003</t>
-  </si>
-  <si>
-    <t>0.0052,0.0801,0.9814,0.0021</t>
-  </si>
-  <si>
-    <t>0.0055,0.0018,0.9858,0.0121</t>
-  </si>
-  <si>
-    <t>0.0089,0.0342,0.9872,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0037,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0048,0.0152,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.9965,0.0012</t>
-  </si>
-  <si>
-    <t>0.6845,0.0039,0.4878,0.0015</t>
-  </si>
-  <si>
-    <t>0.3908,0.0120,0.7746,0.0022</t>
-  </si>
-  <si>
-    <t>0.8043,0.1239,0.0907,0.0076</t>
-  </si>
-  <si>
-    <t>0.5439,0.0964,0.3209,0.0016</t>
-  </si>
-  <si>
-    <t>0.1376,0.4395,0.3028,0.0021</t>
-  </si>
-  <si>
-    <t>0.8899,0.0138,0.1267,0.0007</t>
-  </si>
-  <si>
-    <t>0.7193,0.0182,0.3834,0.0092</t>
-  </si>
-  <si>
-    <t>0.8069,0.0053,0.3070,0.0042</t>
-  </si>
-  <si>
-    <t>0.9155,0.2357,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.1483,0.9314,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9904,0.0151,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9733,0.0440,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9441,0.0906,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.9726,0.0082,0.0162,0.0018</t>
-  </si>
-  <si>
-    <t>0.9572,0.0035,0.0393,0.0031</t>
-  </si>
-  <si>
-    <t>0.9805,0.0004,0.0041,0.0069</t>
-  </si>
-  <si>
-    <t>0.5930,0.0622,0.4248,0.0135</t>
-  </si>
-  <si>
-    <t>0.9488,0.0099,0.0105,0.0123</t>
-  </si>
-  <si>
-    <t>0.0035,0.0074,0.9839,0.0124</t>
-  </si>
-  <si>
-    <t>0.0084,0.2386,0.8331,0.0105</t>
-  </si>
-  <si>
-    <t>0.0247,0.2550,0.8902,0.0189</t>
-  </si>
-  <si>
-    <t>0.7360,0.0018,0.4899,0.0006</t>
-  </si>
-  <si>
-    <t>0.0018,0.0131,0.9868,0.0022</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9952,0.0013,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9961,0.0015,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9931,0.0067,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9875,0.0113,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9846,0.0171,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9968,0.0009,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0221,0.9892,0.0107</t>
-  </si>
-  <si>
-    <t>0.0540,0.0859,0.8830,0.0310</t>
-  </si>
-  <si>
-    <t>0.9192,0.0051,0.0404,0.0204</t>
-  </si>
-  <si>
-    <t>0.0085,0.0009,0.9926,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.0006,0.9968,0.0008</t>
-  </si>
-  <si>
-    <t>0.0055,0.1018,0.9652,0.0047</t>
-  </si>
-  <si>
-    <t>0.0078,0.0005,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0057,0.0015,0.9899,0.0011</t>
-  </si>
-  <si>
-    <t>0.0173,0.0169,0.9874,0.0008</t>
-  </si>
-  <si>
-    <t>0.0150,0.0220,0.9522,0.0158</t>
-  </si>
-  <si>
-    <t>0.0219,0.0398,0.9425,0.0048</t>
-  </si>
-  <si>
-    <t>0.8555,0.0031,0.2014,0.0043</t>
-  </si>
-  <si>
-    <t>0.9144,0.0013,0.1701,0.0006</t>
-  </si>
-  <si>
-    <t>0.9947,0.0008,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0047,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0011,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9794,0.0168,0.0066,0.0009</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0035,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0011,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0026,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0182,0.0028,0.9835,0.0004</t>
-  </si>
-  <si>
-    <t>0.0069,0.0255,0.9863,0.0009</t>
-  </si>
-  <si>
-    <t>0.0102,0.0333,0.9551,0.0112</t>
-  </si>
-  <si>
-    <t>0.0172,0.0087,0.9753,0.0015</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.9958,0.0009</t>
-  </si>
-  <si>
-    <t>0.0486,0.0097,0.9260,0.0262</t>
-  </si>
-  <si>
-    <t>0.0283,0.0159,0.9301,0.0448</t>
-  </si>
-  <si>
-    <t>0.0091,0.0018,0.9624,0.0424</t>
-  </si>
-  <si>
-    <t>0.9876,0.0002,0.0002,0.0199</t>
-  </si>
-  <si>
-    <t>0.0085,0.0938,0.0012,0.9866</t>
-  </si>
-  <si>
-    <t>0.1768,0.0006,0.0033,0.9164</t>
-  </si>
-  <si>
-    <t>0.0135,0.0003,0.0004,0.9955</t>
-  </si>
-  <si>
-    <t>0.0088,0.0006,0.0008,0.9959</t>
-  </si>
-  <si>
-    <t>0.6678,0.0498,0.0011,0.1988</t>
+    <t>0.9967,0.0005,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0004,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9748,0.0171,0.0082,0.0028</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.8197,0.1724,0.0003,0.0043</t>
+  </si>
+  <si>
+    <t>0.8351,0.2623,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9349,0.1083,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9411,0.0246,0.0442,0.0099</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9867,0.0080,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9969,0.0025,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9897,0.0083,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.0021,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.9922,0.0058,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0035,0.9941,0.0006</t>
+  </si>
+  <si>
+    <t>0.0072,0.0527,0.9805,0.0020</t>
+  </si>
+  <si>
+    <t>0.0204,0.0012,0.9855,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.0334,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.0048,0.0127,0.9910,0.0003</t>
+  </si>
+  <si>
+    <t>0.0180,0.0031,0.9856,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.0018,0.9949,0.0010</t>
+  </si>
+  <si>
+    <t>0.0491,0.0118,0.9462,0.0024</t>
+  </si>
+  <si>
+    <t>0.3014,0.0030,0.8924,0.0003</t>
+  </si>
+  <si>
+    <t>0.7913,0.0073,0.2759,0.0032</t>
+  </si>
+  <si>
+    <t>0.6467,0.0649,0.2604,0.0012</t>
+  </si>
+  <si>
+    <t>0.5900,0.1708,0.1299,0.0007</t>
+  </si>
+  <si>
+    <t>0.7504,0.0416,0.2223,0.0031</t>
+  </si>
+  <si>
+    <t>0.8347,0.0047,0.1709,0.0096</t>
+  </si>
+  <si>
+    <t>0.8027,0.0043,0.2977,0.0052</t>
+  </si>
+  <si>
+    <t>0.5883,0.6537,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.2844,0.8702,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9496,0.0744,0.0025,0.0024</t>
+  </si>
+  <si>
+    <t>0.9901,0.0160,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.8676,0.2519,0.0026,0.0010</t>
+  </si>
+  <si>
+    <t>0.8218,0.0986,0.0068,0.0279</t>
+  </si>
+  <si>
+    <t>0.9852,0.0031,0.0076,0.0007</t>
+  </si>
+  <si>
+    <t>0.9452,0.0014,0.0764,0.0023</t>
+  </si>
+  <si>
+    <t>0.9492,0.0098,0.0401,0.0034</t>
+  </si>
+  <si>
+    <t>0.8562,0.0174,0.0468,0.0529</t>
+  </si>
+  <si>
+    <t>0.0113,0.0053,0.9816,0.0028</t>
+  </si>
+  <si>
+    <t>0.0013,0.0217,0.9855,0.0030</t>
+  </si>
+  <si>
+    <t>0.0129,0.1799,0.9581,0.0083</t>
+  </si>
+  <si>
+    <t>0.1650,0.0110,0.8748,0.0030</t>
+  </si>
+  <si>
+    <t>0.0020,0.0198,0.9903,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9907,0.0060,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9927,0.0034,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9935,0.0040,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0030,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9801,0.0239,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.0024,0.9887,0.0163</t>
+  </si>
+  <si>
+    <t>0.0661,0.2584,0.6956,0.0257</t>
+  </si>
+  <si>
+    <t>0.9478,0.0021,0.0341,0.0085</t>
+  </si>
+  <si>
+    <t>0.0631,0.0016,0.9775,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.0056,0.9885,0.0005</t>
+  </si>
+  <si>
+    <t>0.0152,0.0244,0.9706,0.0013</t>
+  </si>
+  <si>
+    <t>0.0076,0.0024,0.9913,0.0016</t>
+  </si>
+  <si>
+    <t>0.0118,0.0063,0.9794,0.0028</t>
+  </si>
+  <si>
+    <t>0.0027,0.0254,0.9923,0.0014</t>
+  </si>
+  <si>
+    <t>0.0095,0.0018,0.9877,0.0022</t>
+  </si>
+  <si>
+    <t>0.0297,0.0161,0.9474,0.0043</t>
+  </si>
+  <si>
+    <t>0.8311,0.0020,0.1830,0.0091</t>
+  </si>
+  <si>
+    <t>0.7749,0.0039,0.3605,0.0012</t>
+  </si>
+  <si>
+    <t>0.9677,0.0200,0.0041,0.0027</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0085,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9979,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9935,0.0050,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9826,0.0229,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0270,0.0128,0.9596,0.0005</t>
+  </si>
+  <si>
+    <t>0.0122,0.0193,0.9796,0.0008</t>
+  </si>
+  <si>
+    <t>0.0035,0.0104,0.9826,0.0111</t>
+  </si>
+  <si>
+    <t>0.0133,0.0098,0.9754,0.0015</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9967,0.0013</t>
+  </si>
+  <si>
+    <t>0.1076,0.0384,0.7579,0.1500</t>
+  </si>
+  <si>
+    <t>0.0077,0.0029,0.9715,0.0391</t>
+  </si>
+  <si>
+    <t>0.0026,0.0031,0.9872,0.0169</t>
+  </si>
+  <si>
+    <t>0.9613,0.0006,0.0005,0.0688</t>
+  </si>
+  <si>
+    <t>0.0175,0.1418,0.0009,0.9730</t>
+  </si>
+  <si>
+    <t>0.1556,0.0010,0.0012,0.9354</t>
+  </si>
+  <si>
+    <t>0.0015,0.0005,0.0028,0.9978</t>
+  </si>
+  <si>
+    <t>0.0595,0.0002,0.0002,0.9869</t>
+  </si>
+  <si>
+    <t>0.6881,0.0068,0.0129,0.2793</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1990,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2438,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,7 +2449,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2648,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2914,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3107,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,7 +3121,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,7 +3135,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3166,7 +3163,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3600,7 +3597,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3611,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3667,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3922,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4398,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4636,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4650,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4664,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4832,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4902,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5434,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
